--- a/services_forms/007_customer_service_survey--services_forms.xlsx
+++ b/services_forms/007_customer_service_survey--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,7 +441,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
@@ -635,12 +635,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>time_of_day</t>
+          <t>time_of_day_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Time Of Day 2</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -686,7 +686,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>How often do you contact us?</t>
+          <t>Contact Frequency</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -727,12 +727,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>contact_method</t>
+          <t>contact_method_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Contact Method</t>
+          <t>Contact Method 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -750,12 +750,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>time_of_day</t>
+          <t>time_of_day_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Time Of Day 3</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,7 +773,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -796,12 +796,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>customer_service_survey_comments</t>
+          <t>customer_service_survey_comments_2</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Customer Service Comments</t>
+          <t>Customer Service Survey Comments 2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>email_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Email 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,7 +842,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_4</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Do you usually contact us during office hours?</t>
+          <t>Question 4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -911,12 +911,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>customer_service_survey_comments</t>
+          <t>customer_service_survey_comments_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Customer Service Comments</t>
+          <t>Customer Service Survey Comments 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -957,7 +957,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_5</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_6</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_7</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>How long did it take for you to get help?</t>
+          <t>Question 7</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,7 +1072,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>question</t>
+          <t>question_8</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>once_a_month</t>
+          <t>once a month</t>
         </is>
       </c>
     </row>
@@ -1204,7 +1204,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>twice_a_month</t>
+          <t>twice a month</t>
         </is>
       </c>
     </row>
@@ -1221,14 +1221,14 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>once_a_week</t>
+          <t>once a week</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1245,7 +1245,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1262,7 +1262,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>contact_method_choices</t>
+          <t>contact_method_2_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1279,7 +1279,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>question_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1289,14 +1289,14 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>less_than_30_minutes</t>
+          <t>less than 30 minutes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>question_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1306,14 +1306,14 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>30_to_60_minutes</t>
+          <t>30 to 60 minutes</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>question_choices</t>
+          <t>question_2_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1323,14 +1323,14 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>more_than_60_minutes</t>
+          <t>more than 60 minutes</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>question_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>question_choices</t>
+          <t>question_3_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>question_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>question_choices</t>
+          <t>question_4_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
